--- a/MyWebExercise_02App/wwwroot/template/my_template.xlsx
+++ b/MyWebExercise_02App/wwwroot/template/my_template.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="25">
   <si>
     <t xml:space="preserve">系統名稱</t>
   </si>
@@ -65,6 +65,9 @@
     <t xml:space="preserve">可Null</t>
   </si>
   <si>
+    <t xml:space="preserve">自動編號</t>
+  </si>
+  <si>
     <t xml:space="preserve">資料型態</t>
   </si>
   <si>
@@ -81,6 +84,9 @@
   </si>
   <si>
     <t xml:space="preserve">#column.nullable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">#column.autoint</t>
   </si>
   <si>
     <t xml:space="preserve">#column.datatype</t>
@@ -511,16 +517,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="24.75" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="8" width="7.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="8" width="24.57"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="8" width="5.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="8" width="8.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="20.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="41.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="8" width="10.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="8" width="20.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="8" width="20.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="8" width="41.86"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -535,6 +542,7 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
@@ -548,6 +556,7 @@
       <c r="E2" s="2"/>
       <c r="F2" s="2"/>
       <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
@@ -562,45 +571,51 @@
       <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="2" t="s">
         <v>14</v>
       </c>
       <c r="F3" s="6" t="s">
         <v>15</v>
       </c>
       <c r="G3" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="E4" s="9" t="s">
+        <v>21</v>
+      </c>
       <c r="F4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="C1:H1"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="C2:H2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
